--- a/bangladesh_export_processor/samples/EXD 784-63264876 (перевод).xlsx
+++ b/bangladesh_export_processor/samples/EXD 784-63264876 (перевод).xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -453,187 +453,187 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Дата</t>
+          <t>Тип документа</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16/03/2026 wee</t>
+          <t>BILLOF</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16/03/2026 wee</t>
+          <t>BILLOF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Код офиса экспорта</t>
+          <t>Код таможни/тариф</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5 32 Item</t>
+          <t>OFFICE OF</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5 32 Item</t>
+          <t>OFFICE OF</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Наименование экспортера</t>
+          <t>Дата</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vintage Denim</t>
+          <t>16/03/2026 wee</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Винтаге Деним</t>
+          <t>16/03/2026 wee</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Наименование получателя/грузополучателя</t>
+          <t>Наименование экспортера</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GLORIA JEANS</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>АО «КОРПОРАЦИЯ «ГЛОРИЯ ДЖИНС»</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Адрес получателя</t>
+          <t>Регистрационный номер BIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>344090</t>
+          <t>BIN: = 9</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>344090</t>
+          <t>BIN: = 9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Декларант/Агент</t>
+          <t>Наименование получателя/грузополучателя</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T.N. CORPORATION</t>
+          <t>Consignee/Importer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T.N. CORPORATION</t>
+          <t>CONSIGNEE/IMPORTER</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Код агента</t>
+          <t>Декларант/Агент</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>101121479</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>101121479</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Наименование авиакомпании</t>
+          <t>Код валюты</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BDDAC</t>
+          <t>Currency Total</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>БДДАЦ</t>
+          <t>Currency Total</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Код авиакомпании</t>
+          <t>Общая стоимость</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FCA BA 2</t>
+          <t>Value 23 Exch.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FCA BA 2</t>
+          <t>Value 23 Exch.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Код валюты</t>
+          <t>Курс валют</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Currency Total Value</t>
+          <t>122.7000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Currency Total Value</t>
+          <t>122.7000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Курс валют</t>
+          <t>Наименование банка</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>122.7</t>
+          <t>BDDAC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>122.7</t>
+          <t>БДДАЦ</t>
         </is>
       </c>
     </row>
@@ -657,51 +657,204 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Сектор и фонд</t>
+          <t>Порт погрузки</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Garments</t>
+          <t>Place of loading/unioading</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Гарменц</t>
+          <t>Place of loading/unioading</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Номер коносамента</t>
+          <t>Код таможни/выпуска</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Reference 72.00 #759</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Reference 72.00 #759</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Код региона</t>
+          <t>Сектор и фонд</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6 Country of</t>
+          <t>Garments Credit 31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6 Country of</t>
+          <t>Гарменц Цредит 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Описание товара</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Код CPC</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1072 | 000</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1072 | 000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Номер CRF/EXP</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NO # 402</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NO # 402</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>UPIUD</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>62132024017-074</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>62132024017-074</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NMB</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NMB_ 3,318.00 9,920.82</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NMB_ 3,318.00 9,920.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Дополнительная стоимость</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Adjustment 1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Adjustment 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Номер коносамента</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>#759 | A</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>#759 | A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Общая декларируемая стоимость</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>46 item Assessable</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>46 item Assessable</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Регистрационный номер</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>101P0275 GB801171844 B</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>101P0275 GB801171844 B</t>
         </is>
       </c>
     </row>

--- a/bangladesh_export_processor/samples/EXD 784-63264876 (перевод).xlsx
+++ b/bangladesh_export_processor/samples/EXD 784-63264876 (перевод).xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -555,306 +555,323 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Декларант/Агент</t>
+          <t>Страна происхождения</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Бангладеш</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Код валюты</t>
+          <t>Декларант/Агент</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Currency Total</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Currency Total</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Общая стоимость</t>
+          <t>Код валюты</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Value 23 Exch.</t>
+          <t>Currency Total</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Value 23 Exch.</t>
+          <t>Currency Total</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Курс валют</t>
+          <t>Общая стоимость</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>122.7000</t>
+          <t>Value 23 Exch.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>122.7000</t>
+          <t>Value 23 Exch.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Наименование банка</t>
+          <t>Курс валют</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BDDAC</t>
+          <t>122.7000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>БДДАЦ</t>
+          <t>122.7000</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Код банка</t>
+          <t>Наименование банка</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BDDAC Dhaka 4</t>
+          <t>BDDAC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BDDAC Dhaka 4</t>
+          <t>БДДАЦ</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Порт погрузки</t>
+          <t>Код банка</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Place of loading/unioading</t>
+          <t>BDDAC Dhaka 4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Place of loading/unioading</t>
+          <t>BDDAC Dhaka 4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Код таможни/выпуска</t>
+          <t>Порт погрузки</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Place of loading/unioading</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Place of loading/unioading</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Сектор и фонд</t>
+          <t>Код таможни/выпуска</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Garments Credit 31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Гарменц Цредит 31</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Описание товара</t>
+          <t>Сектор и фонд</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Goods</t>
+          <t>Garments Credit 31</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Goods</t>
+          <t>Гарменц Цредит 31</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Код CPC</t>
+          <t>Описание товара</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1072 | 000</t>
+          <t>Goods</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1072 | 000</t>
+          <t>Goods</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Номер CRF/EXP</t>
+          <t>Код CPC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NO # 402</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NO # 402</t>
+          <t>1072</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UPIUD</t>
+          <t>Номер CRF/EXP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>62132024017-074</t>
+          <t>NO # 402</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>62132024017-074</t>
+          <t>NO # 402</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NMB</t>
+          <t>UPIUD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NMB_ 3,318.00 9,920.82</t>
+          <t>62132024017-074</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NMB_ 3,318.00 9,920.82</t>
+          <t>62132024017-074</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Дополнительная стоимость</t>
+          <t>NMB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Adjustment 1</t>
+          <t>72.00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Adjustment 1</t>
+          <t>72.00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Номер коносамента</t>
+          <t>Дополнительная стоимость</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>#759 | A</t>
+          <t>Adjustment 1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>#759 | A</t>
+          <t>Adjustment 1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Общая декларируемая стоимость</t>
+          <t>Номер коносамента</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>46 item Assessable</t>
+          <t>#759 | A</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>46 item Assessable</t>
+          <t>#759 | A</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Общая декларируемая стоимость</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>46 item Assessable</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>46 item Assessable</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Регистрационный номер</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>101P0275 GB801171844 B</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>101P0275 GB801171844 B</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>101P0275</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>101P0275</t>
         </is>
       </c>
     </row>

--- a/bangladesh_export_processor/samples/EXD 784-63264876 (перевод).xlsx
+++ b/bangladesh_export_processor/samples/EXD 784-63264876 (перевод).xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -453,423 +453,474 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Тип документа</t>
+          <t>Номер документа</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BILLOF</t>
+          <t>101P0275</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BILLOF</t>
+          <t>101P0275</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Код таможни/тариф</t>
+          <t>Тип документа</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OFFICE OF</t>
+          <t>BILLOF</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>OFFICE OF</t>
+          <t>BILLOF</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Дата</t>
+          <t>Код таможни/тариф</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16/03/2026 wee</t>
+          <t>OFFICE OF</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16/03/2026 wee</t>
+          <t>OFFICE OF</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Наименование экспортера</t>
+          <t>Дата</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16/03/2026 wee</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16/03/2026 wee</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Регистрационный номер BIN</t>
+          <t>Наименование экспортера</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BIN: = 9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BIN: = 9</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Наименование получателя/грузополучателя</t>
+          <t>Регистрационный номер BIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Consignee/Importer</t>
+          <t>BIN: = 9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CONSIGNEE/IMPORTER</t>
+          <t>BIN: = 9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Страна происхождения</t>
+          <t>Наименование получателя/грузополучателя</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Consignee/Importer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Бангладеш</t>
+          <t>CONSIGNEE/IMPORTER</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Декларант/Агент</t>
+          <t>Страна происхождения</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Бангладеш</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Код валюты</t>
+          <t>Декларант/Агент</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Currency Total</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Currency Total</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Общая стоимость</t>
+          <t>Условия поставки</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Value 23 Exch.</t>
+          <t>FCA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Value 23 Exch.</t>
+          <t>FCA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Курс валют</t>
+          <t>Код валюты</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>122.7000</t>
+          <t>Currency Total</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>122.7000</t>
+          <t>Currency Total</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Наименование банка</t>
+          <t>Общая стоимость</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BDDAC</t>
+          <t>Value 23 Exch.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>БДДАЦ</t>
+          <t>Value 23 Exch.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Код банка</t>
+          <t>Курс валют</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BDDAC Dhaka 4</t>
+          <t>122.7000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BDDAC Dhaka 4</t>
+          <t>122.7000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Порт погрузки</t>
+          <t>Наименование банка</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Place of loading/unioading</t>
+          <t>BDDAC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Place of loading/unioading</t>
+          <t>БДДАЦ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Код таможни/выпуска</t>
+          <t>Код банка</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>BDDAC Dhaka 4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>BDDAC Dhaka 4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Сектор и фонд</t>
+          <t>Порт погрузки</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Garments Credit 31</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Гарменц Цредит 31</t>
+          <t>DAC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Описание товара</t>
+          <t>Код таможни/выпуска</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Goods</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Goods</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Код CPC</t>
+          <t>Сектор и фонд</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>Garments Credit 31</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>Гарменц Цредит 31</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Номер CRF/EXP</t>
+          <t>Описание товара</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NO # 402</t>
+          <t>Goods</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NO # 402</t>
+          <t>Goods</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UPIUD</t>
+          <t>Код CPC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>62132024017-074</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>62132024017-074</t>
+          <t>1072</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NMB</t>
+          <t>Номер CRF/EXP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>72.00</t>
+          <t>NO # 402</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>72.00</t>
+          <t>NO # 402</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Дополнительная стоимость</t>
+          <t>Дата CRF/EXP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Adjustment 1</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Adjustment 1</t>
+          <t>16/03/2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Номер коносамента</t>
+          <t>UPIUD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>#759 | A</t>
+          <t>62132024017-074</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>#759 | A</t>
+          <t>62132024017-074</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Общая декларируемая стоимость</t>
+          <t>NMB</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>46 item Assessable</t>
+          <t>72.00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>46 item Assessable</t>
+          <t>72.00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Дополнительная стоимость</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Adjustment 1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Adjustment 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Номер коносамента</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>#759 | A</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>#759 | A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Общая декларируемая стоимость</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>46 item Assessable</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>46 item Assessable</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Регистрационный номер</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>101P0275</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>101P0275</t>
         </is>

--- a/bangladesh_export_processor/samples/EXD 784-63264876 (перевод).xlsx
+++ b/bangladesh_export_processor/samples/EXD 784-63264876 (перевод).xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -572,355 +572,389 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Страна происхождения</t>
+          <t>Адрес получателя</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>STACHKI AVENUE 184,344090 ROSTOV-ON-DON</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Бангладеш</t>
+          <t>STACHKI пр. 184, 344090, Россия</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Декларант/Агент</t>
+          <t>Страна происхождения</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Бангладеш</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Условия поставки</t>
+          <t>Декларант/Агент</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FCA</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FCA</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Код валюты</t>
+          <t>Адрес декларанта/агента</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Currency Total</t>
+          <t>MALIBAG, ROOM NO 402, DHAKA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Currency Total</t>
+          <t>МАЛИБАГ, РООМ НО 402, ДХАКА</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Общая стоимость</t>
+          <t>Условия поставки</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Value 23 Exch.</t>
+          <t>FCA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Value 23 Exch.</t>
+          <t>FCA</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Курс валют</t>
+          <t>Код валюты</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>122.7000</t>
+          <t>Currency Total</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>122.7000</t>
+          <t>Currency Total</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Наименование банка</t>
+          <t>Общая стоимость</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BDDAC</t>
+          <t>Value 23 Exch.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>БДДАЦ</t>
+          <t>Value 23 Exch.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Код банка</t>
+          <t>Курс валют</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BDDAC Dhaka 4</t>
+          <t>122.7000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BDDAC Dhaka 4</t>
+          <t>122.7000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Порт погрузки</t>
+          <t>Наименование банка</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>BDDAC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>БДДАЦ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Код таможни/выпуска</t>
+          <t>Код банка</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>BDDAC Dhaka 4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>BDDAC Dhaka 4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Сектор и фонд</t>
+          <t>Порт погрузки</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Garments Credit 31</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Гарменц Цредит 31</t>
+          <t>DAC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Описание товара</t>
+          <t>Код таможни/выпуска</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Goods</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Goods</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Код CPC</t>
+          <t>Сектор и фонд</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>Garments Credit 31</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>Гарменц Цредит 31</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Номер CRF/EXP</t>
+          <t>Описание товара</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NO # 402</t>
+          <t>Goods</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NO # 402</t>
+          <t>Goods</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Дата CRF/EXP</t>
+          <t>Код CPC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>1072</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UPIUD</t>
+          <t>Номер CRF/EXP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>62132024017-074</t>
+          <t>NO # 402</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>62132024017-074</t>
+          <t>NO # 402</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NMB</t>
+          <t>Дата CRF/EXP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>72.00</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>72.00</t>
+          <t>16/03/2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Дополнительная стоимость</t>
+          <t>UPIUD</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Adjustment 1</t>
+          <t>62132024017-074</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Adjustment 1</t>
+          <t>62132024017-074</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Номер коносамента</t>
+          <t>NMB</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>#759 | A</t>
+          <t>72.00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>#759 | A</t>
+          <t>72.00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Общая декларируемая стоимость</t>
+          <t>Дополнительная стоимость</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>46 item Assessable</t>
+          <t>Adjustment 1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>46 item Assessable</t>
+          <t>Adjustment 1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Номер коносамента</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>#759 | A</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>#759 | A</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Общая декларируемая стоимость</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>46 item Assessable</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>46 item Assessable</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Регистрационный номер</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>101P0275</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>101P0275</t>
         </is>
